--- a/Tennis_Spielplan_Google_Drive_Native_Fix.xlsx
+++ b/Tennis_Spielplan_Google_Drive_Native_Fix.xlsx
@@ -1134,6 +1134,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -1209,7 +1210,7 @@
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="M4" s="16" t="inlineStr">
@@ -1609,7 +1610,7 @@
       <c r="N9" s="30" t="inlineStr"/>
       <c r="O9" s="45" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="P9" s="46" t="inlineStr">
@@ -1783,7 +1784,7 @@
       <c r="J11" s="30" t="inlineStr"/>
       <c r="K11" s="45" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="L11" s="28" t="inlineStr">
@@ -1862,7 +1863,7 @@
       <c r="F12" s="30" t="inlineStr"/>
       <c r="G12" s="45" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="H12" s="28" t="inlineStr">
@@ -1941,7 +1942,7 @@
       </c>
       <c r="C13" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
@@ -2004,7 +2005,7 @@
       </c>
       <c r="R13" s="67" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="S13" s="60" t="inlineStr">
@@ -2308,7 +2309,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2465,7 @@
       <c r="N18" s="30" t="inlineStr"/>
       <c r="O18" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="P18" s="87" t="inlineStr">
@@ -2638,7 +2639,7 @@
       <c r="J20" s="30" t="inlineStr"/>
       <c r="K20" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="L20" s="28" t="inlineStr">
@@ -2717,7 +2718,7 @@
       <c r="F21" s="30" t="inlineStr"/>
       <c r="G21" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
@@ -2796,7 +2797,7 @@
       </c>
       <c r="C22" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
@@ -2859,7 +2860,7 @@
       </c>
       <c r="R22" s="67" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="S22" s="60" t="inlineStr">
@@ -3294,7 +3295,7 @@
       <c r="N27" s="30" t="inlineStr"/>
       <c r="O27" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="P27" s="87" t="inlineStr">
@@ -3458,7 +3459,7 @@
       <c r="J29" s="30" t="inlineStr"/>
       <c r="K29" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="L29" s="28" t="inlineStr">
@@ -3532,7 +3533,7 @@
       <c r="F30" s="30" t="inlineStr"/>
       <c r="G30" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="H30" s="28" t="inlineStr">
@@ -3606,7 +3607,7 @@
       </c>
       <c r="C31" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -3669,7 +3670,7 @@
       </c>
       <c r="R31" s="67" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="S31" s="60" t="inlineStr">
@@ -4104,7 +4105,7 @@
       <c r="N36" s="30" t="inlineStr"/>
       <c r="O36" s="59" t="inlineStr">
         <is>
-          <t>Wojtanowtisch</t>
+          <t>Wojtanowitsch</t>
         </is>
       </c>
       <c r="P36" s="87" t="inlineStr">
